--- a/excel-files/LAS PINAS/EQUITABLE VILLAGE NATIONAL HIGH SCHOOL.xlsx
+++ b/excel-files/LAS PINAS/EQUITABLE VILLAGE NATIONAL HIGH SCHOOL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="196" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FB813DF-AED1-4881-97EF-B6D42ECD1A95}"/>
+  <xr:revisionPtr revIDLastSave="241" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{244C93B0-4D28-4DEB-9F16-47996434EE9C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5418,15 +5418,12 @@
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{C493EEDA-8E42-4A0F-9FBE-7DAF2710166C}">
-      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5663,7 +5660,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="38.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -6215,7 +6212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6228,7 +6225,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="38.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6780,7 +6777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6794,7 +6791,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="38.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -7415,7 +7412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7429,7 +7426,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -8050,7 +8047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8064,7 +8061,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8685,7 +8682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8699,7 +8696,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -10009,7 +10006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -10698,7 +10695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -11387,7 +11384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -12642,7 +12639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12653,7 +12650,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -13604,7 +13601,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="31"/>
-      <c r="L127" s="29"/>
+      <c r="L127" s="1"/>
       <c r="M127" s="31"/>
       <c r="N127" s="5">
         <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
@@ -13616,7 +13613,7 @@
       </c>
       <c r="P127" s="5"/>
       <c r="Q127" s="31"/>
-      <c r="R127" s="29"/>
+      <c r="R127" s="1"/>
       <c r="S127" s="31"/>
       <c r="T127" s="5">
         <f t="shared" si="18"/>
@@ -13631,7 +13628,7 @@
         <v>0</v>
       </c>
       <c r="W127" s="31"/>
-      <c r="X127" s="29"/>
+      <c r="X127" s="1"/>
       <c r="Y127" s="31"/>
       <c r="Z127" s="5">
         <f t="shared" si="20"/>
@@ -13825,7 +13822,7 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C103:C110 C112:C127 C5:C12 C63:C71 C73:C81 C83:C91 C93:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 Q14:R21 W14:X21 Q23:R31 W23:X31 H33:I41 Q33:R41 W33:X41 H43:I51 Q43:R51 W43:X51 H53:I61 Q53:R61 W53:X61 H63:I71 Q63:R71 W63:X71 H73:I81 Q73:R81 W73:X81 H83:I91 Q83:R91 W83:X91 H93:I101 Q93:R101 W93:X101 H103:I110 Q103:R110 W103:X110 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 G6 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D5:F12 D14:F21 D23:F31 D33:F41 D43:F51 D53:F61 D63:F71 D73:F81 D83:F91 D93:F101 D103:F110 D112:F127" name="LAS"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 H33:I41 H43:I51 H53:I61 H63:I71 H73:I81 H83:I91 H93:I101 H103:I110 H112:I127 N127:Q127 H14:I21 H23:I31 H6:I12 Q112:Q126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 G6 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D5:F12 D14:F21 D23:F31 D33:F41 D43:F51 D53:F61 D63:F71 D73:F81 D83:F91 D93:F101 D103:F110 D112:F127 K6:L12 K63:L71 K103:L110 K112:L127 K14:L21 K23:L31 K33:L41 K43:L51 K53:L61 K73:L81 K83:L91 K93:L101 N5:R12 Q63:R71 Q103:R110 R112:R127 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 Q73:R81 Q83:R91 Q93:R101 T5:X12 W63:X71 W103:X110 W112:X127 W14:X21 W23:X31 W33:X41 W43:X51 W53:X61 W73:X81 W83:X91 W93:X101" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G103:G110 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G5 G7:G12" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -13835,17 +13832,20 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 R103:R110 R83:R91 R93:R101 R14:R21 R5:R12 G6 X103:X110 L103:L110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127" xr:uid="{B3931F86-B852-41CE-B400-D187AB696157}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L112:L127 L53:L61 L103:L110 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L83:L91 L93:L101 R112:R127 R53:R61 R103:R110 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R83:R91 R93:R101 X112:X127 X53:X61 X103:X110 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X83:X91 X93:X101" xr:uid="{74019A24-FFA0-497D-8B57-1C334316EBD1}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18796,7 +18796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
+    <row r="78" spans="1:27" s="7" customFormat="1" ht="15"/>
     <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
@@ -20380,7 +20380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="15"/>
     <row r="103" spans="1:27" ht="19.5">
       <c r="A103" s="10">
         <v>10</v>
@@ -22429,7 +22429,7 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C115:C122 C67:C77 C79:C89 C91:C101 C103:C113" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113 D67:F77 D79:F89 D91:F101 D103:F113" name="LAS"/>
+    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 Z67:AA77 Z79:AA89 Z91:AA101 Z103:AA113 N115:R122 T115:X122 Z115:AA122 H115:L122 N31:R41 N43:R53 N55:R65 D67:F77 D79:F89 D91:F101 D103:F113 H67:L77 H79:L89 H91:L101 H103:L113 N67:R77 N103:R113 N79:R89 N91:R101 T67:X77 T79:X89 T91:X101 T103:X113" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -22439,14 +22439,17 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 R115:R122 L115:L122 F55:F65 F3:F10 F115:F122 X115:X122 F12:F19" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 F31:F41 F21:F29 X55:X65 R12:R19 R3:R10 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 F12:F19 X115:X122 L55:L65 F115:F122 F3:F10 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 F43:F53 R115:R122 R55:R65 L115:L122 F55:F65" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F67:F77 F79:F89 F91:F101 F103:F105 F106:F113" xr:uid="{70CDD7E8-C51B-42E6-BEE5-DC227C10C4FD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F67:F77 F79:F89 F91:F101 F103:F113" xr:uid="{70CDD7E8-C51B-42E6-BEE5-DC227C10C4FD}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L67:L77 L79:L89 L91:L101 L103:L113 R103:R113 R67:R77 R79:R89 R91:R101 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{977A1B99-BD5B-4739-8E89-A5E2F9B96765}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
